--- a/SuppXLS/Scen_NoCircularity.xlsx
+++ b/SuppXLS/Scen_NoCircularity.xlsx
@@ -166,7 +166,7 @@
     <t>DirRecy*</t>
   </si>
   <si>
-    <t>Tra_BEV_Batt</t>
+    <t>Tra_BEV_Batt*</t>
   </si>
   <si>
     <t>Tech</t>
@@ -707,13 +707,13 @@
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
+      <sz val="8"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Tahoma"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1840,6 +1840,7 @@
         <v>21</v>
       </c>
     </row>
+    <row r="12" ht="15.25"/>
     <row r="13" ht="15.25" spans="29:40">
       <c r="AC13" s="16"/>
       <c r="AD13" s="16"/>
